--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441257</v>
+        <v>113441240</v>
       </c>
       <c r="B2" t="n">
-        <v>91290</v>
+        <v>91329</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788899</v>
+        <v>788919</v>
       </c>
       <c r="R2" t="n">
-        <v>7216051</v>
+        <v>7216045</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441240</v>
+        <v>113441376</v>
       </c>
       <c r="B3" t="n">
-        <v>91313</v>
+        <v>91306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788919</v>
+        <v>788899</v>
       </c>
       <c r="R3" t="n">
-        <v>7216045</v>
+        <v>7216051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441354</v>
+        <v>113441235</v>
       </c>
       <c r="B4" t="n">
-        <v>91282</v>
+        <v>91298</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441240</v>
+        <v>113441354</v>
       </c>
       <c r="B2" t="n">
-        <v>91329</v>
+        <v>91298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788919</v>
+        <v>788870</v>
       </c>
       <c r="R2" t="n">
-        <v>7216045</v>
+        <v>7216068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441235</v>
+        <v>113441359</v>
       </c>
       <c r="B4" t="n">
-        <v>91298</v>
+        <v>91329</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788870</v>
+        <v>788919</v>
       </c>
       <c r="R4" t="n">
-        <v>7216068</v>
+        <v>7216045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441354</v>
+        <v>113441376</v>
       </c>
       <c r="B2" t="n">
-        <v>91298</v>
+        <v>91318</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788870</v>
+        <v>788899</v>
       </c>
       <c r="R2" t="n">
-        <v>7216068</v>
+        <v>7216051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441376</v>
+        <v>113441240</v>
       </c>
       <c r="B3" t="n">
-        <v>91306</v>
+        <v>91341</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788899</v>
+        <v>788919</v>
       </c>
       <c r="R3" t="n">
-        <v>7216051</v>
+        <v>7216045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441359</v>
+        <v>113441354</v>
       </c>
       <c r="B4" t="n">
-        <v>91329</v>
+        <v>91310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788919</v>
+        <v>788870</v>
       </c>
       <c r="R4" t="n">
-        <v>7216045</v>
+        <v>7216068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441376</v>
+        <v>113441235</v>
       </c>
       <c r="B2" t="n">
-        <v>91318</v>
+        <v>91310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788899</v>
+        <v>788870</v>
       </c>
       <c r="R2" t="n">
-        <v>7216051</v>
+        <v>7216068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441240</v>
+        <v>113441359</v>
       </c>
       <c r="B3" t="n">
         <v>91341</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441354</v>
+        <v>113441376</v>
       </c>
       <c r="B4" t="n">
-        <v>91310</v>
+        <v>91318</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788870</v>
+        <v>788899</v>
       </c>
       <c r="R4" t="n">
-        <v>7216068</v>
+        <v>7216051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441235</v>
+        <v>113441359</v>
       </c>
       <c r="B2" t="n">
-        <v>91310</v>
+        <v>91363</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788870</v>
+        <v>788919</v>
       </c>
       <c r="R2" t="n">
-        <v>7216068</v>
+        <v>7216045</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441359</v>
+        <v>113441354</v>
       </c>
       <c r="B3" t="n">
-        <v>91341</v>
+        <v>91332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788919</v>
+        <v>788870</v>
       </c>
       <c r="R3" t="n">
-        <v>7216045</v>
+        <v>7216068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>113441376</v>
       </c>
       <c r="B4" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441359</v>
+        <v>113441257</v>
       </c>
       <c r="B2" t="n">
-        <v>91363</v>
+        <v>91344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788919</v>
+        <v>788899</v>
       </c>
       <c r="R2" t="n">
-        <v>7216045</v>
+        <v>7216051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441354</v>
+        <v>113441235</v>
       </c>
       <c r="B3" t="n">
-        <v>91332</v>
+        <v>91336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441376</v>
+        <v>113441359</v>
       </c>
       <c r="B4" t="n">
-        <v>91340</v>
+        <v>91367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788899</v>
+        <v>788919</v>
       </c>
       <c r="R4" t="n">
-        <v>7216051</v>
+        <v>7216045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441257</v>
+        <v>113441376</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>91350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441235</v>
+        <v>113441359</v>
       </c>
       <c r="B3" t="n">
-        <v>91336</v>
+        <v>91373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788870</v>
+        <v>788919</v>
       </c>
       <c r="R3" t="n">
-        <v>7216068</v>
+        <v>7216045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441359</v>
+        <v>113441235</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>91342</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788919</v>
+        <v>788870</v>
       </c>
       <c r="R4" t="n">
-        <v>7216045</v>
+        <v>7216068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441376</v>
+        <v>113441359</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788899</v>
+        <v>788919</v>
       </c>
       <c r="R2" t="n">
-        <v>7216051</v>
+        <v>7216045</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441359</v>
+        <v>113441376</v>
       </c>
       <c r="B3" t="n">
-        <v>91373</v>
+        <v>91350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788919</v>
+        <v>788899</v>
       </c>
       <c r="R3" t="n">
-        <v>7216045</v>
+        <v>7216051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441359</v>
+        <v>113441240</v>
       </c>
       <c r="B2" t="n">
         <v>91373</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113441240</v>
       </c>
       <c r="B2" t="n">
-        <v>91373</v>
+        <v>91380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441376</v>
+        <v>113441354</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788899</v>
+        <v>788870</v>
       </c>
       <c r="R3" t="n">
-        <v>7216051</v>
+        <v>7216068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441235</v>
+        <v>113441257</v>
       </c>
       <c r="B4" t="n">
-        <v>91342</v>
+        <v>91357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788870</v>
+        <v>788899</v>
       </c>
       <c r="R4" t="n">
-        <v>7216068</v>
+        <v>7216051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441240</v>
+        <v>113441257</v>
       </c>
       <c r="B2" t="n">
-        <v>91380</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788919</v>
+        <v>788899</v>
       </c>
       <c r="R2" t="n">
-        <v>7216045</v>
+        <v>7216051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441354</v>
+        <v>113441359</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>91385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788870</v>
+        <v>788919</v>
       </c>
       <c r="R3" t="n">
-        <v>7216068</v>
+        <v>7216045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441257</v>
+        <v>113441354</v>
       </c>
       <c r="B4" t="n">
-        <v>91357</v>
+        <v>91354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788899</v>
+        <v>788870</v>
       </c>
       <c r="R4" t="n">
-        <v>7216051</v>
+        <v>7216068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441257</v>
+        <v>113441240</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>91413</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788899</v>
+        <v>788919</v>
       </c>
       <c r="R2" t="n">
-        <v>7216051</v>
+        <v>7216045</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441359</v>
+        <v>113441235</v>
       </c>
       <c r="B3" t="n">
-        <v>91385</v>
+        <v>91382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788919</v>
+        <v>788870</v>
       </c>
       <c r="R3" t="n">
-        <v>7216045</v>
+        <v>7216068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441354</v>
+        <v>113441376</v>
       </c>
       <c r="B4" t="n">
-        <v>91354</v>
+        <v>91390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788870</v>
+        <v>788899</v>
       </c>
       <c r="R4" t="n">
-        <v>7216068</v>
+        <v>7216051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441240</v>
+        <v>113441235</v>
       </c>
       <c r="B2" t="n">
-        <v>91413</v>
+        <v>91382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788919</v>
+        <v>788870</v>
       </c>
       <c r="R2" t="n">
-        <v>7216045</v>
+        <v>7216068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441235</v>
+        <v>113441359</v>
       </c>
       <c r="B3" t="n">
-        <v>91382</v>
+        <v>91413</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788870</v>
+        <v>788919</v>
       </c>
       <c r="R3" t="n">
-        <v>7216068</v>
+        <v>7216045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441376</v>
+        <v>113441257</v>
       </c>
       <c r="B4" t="n">
         <v>91390</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441235</v>
+        <v>113441376</v>
       </c>
       <c r="B2" t="n">
-        <v>91382</v>
+        <v>91394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788870</v>
+        <v>788899</v>
       </c>
       <c r="R2" t="n">
-        <v>7216068</v>
+        <v>7216051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>113441359</v>
       </c>
       <c r="B3" t="n">
-        <v>91413</v>
+        <v>91417</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441257</v>
+        <v>113441354</v>
       </c>
       <c r="B4" t="n">
-        <v>91390</v>
+        <v>91386</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>788899</v>
+        <v>788870</v>
       </c>
       <c r="R4" t="n">
-        <v>7216051</v>
+        <v>7216068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41508-2021 artfynd.xlsx
+++ b/artfynd/A 41508-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
